--- a/data/informes/cuadro_10_5.xlsx
+++ b/data/informes/cuadro_10_5.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>23463699.29</v>
+        <v>28230340.21</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>110029.6</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>23573728.89</v>
+        <v>28340369.81</v>
       </c>
     </row>
     <row r="6">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>16354851.89</v>
+        <v>20214769.56</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>16354851.89</v>
+        <v>20214769.56</v>
       </c>
     </row>
     <row r="7">
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>2637350.77</v>
+        <v>2538116.42</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>2637350.77</v>
+        <v>2538116.42</v>
       </c>
     </row>
     <row r="8">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>26090.02</v>
+        <v>59509.36</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>47908.6</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>73998.62</v>
+        <v>107417.96</v>
       </c>
     </row>
     <row r="9">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>3419480.35</v>
+        <v>3993032.02</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>3419480.35</v>
+        <v>3993032.02</v>
       </c>
     </row>
     <row r="10">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1019095.03</v>
+        <v>1418081.62</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1019095.03</v>
+        <v>1418081.62</v>
       </c>
     </row>
     <row r="11">
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>26255180.31</v>
+        <v>31021821.23</v>
       </c>
       <c r="D41" s="10" t="n">
         <v>4022010.07</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>30277190.37</v>
+        <v>35043831.29</v>
       </c>
     </row>
     <row r="42">
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>26255180.31</v>
+        <v>31021821.23</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>4022010.07</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>30277190.37</v>
+        <v>35043831.29</v>
       </c>
     </row>
     <row r="46">
@@ -1402,13 +1402,13 @@
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>34194975.94</v>
+        <v>29666737.76</v>
       </c>
       <c r="D48" s="6" t="n">
         <v>536226.28</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>34731202.22</v>
+        <v>30202964.04</v>
       </c>
     </row>
     <row r="49">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>24259329.67</v>
+        <v>20629906.84</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>24259329.67</v>
+        <v>20629906.84</v>
       </c>
     </row>
     <row r="50">
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>3088429.71</v>
+        <v>3057447.39</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>4801.95</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>3093231.66</v>
+        <v>3062249.34</v>
       </c>
     </row>
     <row r="52">
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>3829083.64</v>
+        <v>3323709.29</v>
       </c>
       <c r="D52" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>3829083.64</v>
+        <v>3323709.29</v>
       </c>
     </row>
     <row r="53">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>2400424.6</v>
+        <v>2037965.92</v>
       </c>
       <c r="D53" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>2400424.6</v>
+        <v>2037965.92</v>
       </c>
     </row>
     <row r="54">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>34834512.57</v>
+        <v>30306274.39</v>
       </c>
       <c r="D84" s="10" t="n">
         <v>2832055.18</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>37666567.75</v>
+        <v>33138329.57</v>
       </c>
     </row>
     <row r="85">
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>34834512.57</v>
+        <v>30306274.39</v>
       </c>
       <c r="D87" s="10" t="n">
         <v>2832055.18</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>37666567.75</v>
+        <v>33138329.57</v>
       </c>
     </row>
     <row r="89">
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="C91" s="6" t="n">
-        <v>17573059.23</v>
+        <v>17083760.34</v>
       </c>
       <c r="D91" s="6" t="n">
         <v>1466749.27</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>19039808.5</v>
+        <v>18550509.61</v>
       </c>
     </row>
     <row r="92">
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>6512694.38</v>
+        <v>6173152.63</v>
       </c>
       <c r="D92" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>6512694.38</v>
+        <v>6173152.63</v>
       </c>
     </row>
     <row r="93">
@@ -2302,13 +2302,13 @@
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>2100449.36</v>
+        <v>2047253.51</v>
       </c>
       <c r="D93" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>2100449.36</v>
+        <v>2047253.51</v>
       </c>
     </row>
     <row r="94">
@@ -2323,13 +2323,13 @@
         </is>
       </c>
       <c r="C94" s="8" t="n">
-        <v>5154511.86</v>
+        <v>5154366.7</v>
       </c>
       <c r="D94" s="8" t="n">
         <v>339568.43</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>5494080.29</v>
+        <v>5493935.13</v>
       </c>
     </row>
     <row r="95">
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>2931816.01</v>
+        <v>2891873.41</v>
       </c>
       <c r="D95" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>2931816.01</v>
+        <v>2891873.41</v>
       </c>
     </row>
     <row r="96">
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>621516.13</v>
+        <v>565042.6</v>
       </c>
       <c r="D96" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>621516.13</v>
+        <v>565042.6</v>
       </c>
     </row>
     <row r="97">
@@ -3012,13 +3012,13 @@
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>19796979.1</v>
+        <v>19307680.21</v>
       </c>
       <c r="D127" s="10" t="n">
         <v>6068958.33</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>25865937.42</v>
+        <v>25376638.53</v>
       </c>
     </row>
     <row r="128">
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>19796979.1</v>
+        <v>19307680.21</v>
       </c>
       <c r="D130" s="10" t="n">
         <v>6068958.33</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>25865937.42</v>
+        <v>25376638.53</v>
       </c>
     </row>
     <row r="132">
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>8581278.74</v>
+        <v>8507962.880000001</v>
       </c>
       <c r="D134" s="6" t="n">
         <v>45763.01</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>8627041.75</v>
+        <v>8553725.890000001</v>
       </c>
     </row>
     <row r="135">
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>100483.79</v>
+        <v>102384.33</v>
       </c>
       <c r="D135" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>100483.79</v>
+        <v>102384.33</v>
       </c>
     </row>
     <row r="136">
@@ -3160,13 +3160,13 @@
         </is>
       </c>
       <c r="C136" s="8" t="n">
-        <v>6729262.96</v>
+        <v>6668990.07</v>
       </c>
       <c r="D136" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E136" s="8" t="n">
-        <v>6729262.96</v>
+        <v>6668990.07</v>
       </c>
     </row>
     <row r="137">
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="C138" s="8" t="n">
-        <v>1691726.33</v>
+        <v>1676782.82</v>
       </c>
       <c r="D138" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E138" s="8" t="n">
-        <v>1691726.33</v>
+        <v>1676782.82</v>
       </c>
     </row>
     <row r="139">
@@ -3870,13 +3870,13 @@
         </is>
       </c>
       <c r="C170" s="10" t="n">
-        <v>9472955.689999999</v>
+        <v>9399639.83</v>
       </c>
       <c r="D170" s="10" t="n">
         <v>1496714.99</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>10969670.68</v>
+        <v>10896354.82</v>
       </c>
     </row>
     <row r="171">
@@ -3921,13 +3921,13 @@
         </is>
       </c>
       <c r="C173" s="10" t="n">
-        <v>9472955.689999999</v>
+        <v>9399639.83</v>
       </c>
       <c r="D173" s="10" t="n">
         <v>1496714.99</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>10969670.68</v>
+        <v>10896354.82</v>
       </c>
     </row>
     <row r="175">
@@ -3976,13 +3976,13 @@
         </is>
       </c>
       <c r="C177" s="6" t="n">
-        <v>2331299.19</v>
+        <v>2327149.81</v>
       </c>
       <c r="D177" s="6" t="n">
         <v>24069.71</v>
       </c>
       <c r="E177" s="6" t="n">
-        <v>2355368.9</v>
+        <v>2351219.52</v>
       </c>
     </row>
     <row r="178">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>1800652.61</v>
+        <v>1797367.91</v>
       </c>
       <c r="D179" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E179" s="8" t="n">
-        <v>1800652.61</v>
+        <v>1797367.91</v>
       </c>
     </row>
     <row r="180">
@@ -4060,13 +4060,13 @@
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>479694.87</v>
+        <v>478830.19</v>
       </c>
       <c r="D181" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E181" s="8" t="n">
-        <v>479694.87</v>
+        <v>478830.19</v>
       </c>
     </row>
     <row r="182">
@@ -4728,13 +4728,13 @@
         </is>
       </c>
       <c r="C213" s="10" t="n">
-        <v>3072184.57</v>
+        <v>3068035.19</v>
       </c>
       <c r="D213" s="10" t="n">
         <v>2082891.57</v>
       </c>
       <c r="E213" s="10" t="n">
-        <v>5155076.14</v>
+        <v>5150926.76</v>
       </c>
     </row>
     <row r="214">
@@ -4779,13 +4779,13 @@
         </is>
       </c>
       <c r="C216" s="10" t="n">
-        <v>3072184.57</v>
+        <v>3068035.19</v>
       </c>
       <c r="D216" s="10" t="n">
         <v>2082891.57</v>
       </c>
       <c r="E216" s="10" t="n">
-        <v>5155076.14</v>
+        <v>5150926.76</v>
       </c>
     </row>
     <row r="218">
@@ -4834,13 +4834,13 @@
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>20817864.32</v>
+        <v>20735474.68</v>
       </c>
       <c r="D220" s="6" t="n">
         <v>279076.91</v>
       </c>
       <c r="E220" s="6" t="n">
-        <v>21096941.23</v>
+        <v>21014551.59</v>
       </c>
     </row>
     <row r="221">
@@ -4855,13 +4855,13 @@
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>1478220.14</v>
+        <v>1538303.98</v>
       </c>
       <c r="D221" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E221" s="8" t="n">
-        <v>1478220.14</v>
+        <v>1538303.98</v>
       </c>
     </row>
     <row r="222">
@@ -4876,13 +4876,13 @@
         </is>
       </c>
       <c r="C222" s="8" t="n">
-        <v>13366334.66</v>
+        <v>13245948</v>
       </c>
       <c r="D222" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E222" s="8" t="n">
-        <v>13366334.66</v>
+        <v>13245948</v>
       </c>
     </row>
     <row r="223">
@@ -4897,13 +4897,13 @@
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>1852175.76</v>
+        <v>1852184.67</v>
       </c>
       <c r="D223" s="8" t="n">
         <v>30144.92</v>
       </c>
       <c r="E223" s="8" t="n">
-        <v>1882320.68</v>
+        <v>1882329.59</v>
       </c>
     </row>
     <row r="224">
@@ -4918,13 +4918,13 @@
         </is>
       </c>
       <c r="C224" s="8" t="n">
-        <v>3913077.34</v>
+        <v>3884976.34</v>
       </c>
       <c r="D224" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E224" s="8" t="n">
-        <v>3913077.34</v>
+        <v>3884976.34</v>
       </c>
     </row>
     <row r="225">
@@ -4939,13 +4939,13 @@
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>175902.28</v>
+        <v>181907.55</v>
       </c>
       <c r="D225" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E225" s="8" t="n">
-        <v>175902.28</v>
+        <v>181907.55</v>
       </c>
     </row>
     <row r="226">
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="C256" s="10" t="n">
-        <v>21781245.83</v>
+        <v>21698856.19</v>
       </c>
       <c r="D256" s="10" t="n">
         <v>11357283.32</v>
       </c>
       <c r="E256" s="10" t="n">
-        <v>33138529.15</v>
+        <v>33056139.51</v>
       </c>
     </row>
     <row r="257">
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="C259" s="10" t="n">
-        <v>21781245.83</v>
+        <v>21698856.19</v>
       </c>
       <c r="D259" s="10" t="n">
         <v>11357283.32</v>
       </c>
       <c r="E259" s="10" t="n">
-        <v>33138529.15</v>
+        <v>33056139.51</v>
       </c>
     </row>
     <row r="261">
@@ -6550,13 +6550,13 @@
         </is>
       </c>
       <c r="C306" s="6" t="n">
-        <v>0</v>
+        <v>1512579.24</v>
       </c>
       <c r="D306" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E306" s="6" t="n">
-        <v>0</v>
+        <v>1512579.24</v>
       </c>
     </row>
     <row r="307">
@@ -6571,13 +6571,13 @@
         </is>
       </c>
       <c r="C307" s="8" t="n">
-        <v>0</v>
+        <v>897414</v>
       </c>
       <c r="D307" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E307" s="8" t="n">
-        <v>0</v>
+        <v>897414</v>
       </c>
     </row>
     <row r="308">
@@ -6592,13 +6592,13 @@
         </is>
       </c>
       <c r="C308" s="8" t="n">
-        <v>0</v>
+        <v>336374.45</v>
       </c>
       <c r="D308" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E308" s="8" t="n">
-        <v>0</v>
+        <v>336374.45</v>
       </c>
     </row>
     <row r="309">
@@ -6634,13 +6634,13 @@
         </is>
       </c>
       <c r="C310" s="8" t="n">
-        <v>0</v>
+        <v>190387.81</v>
       </c>
       <c r="D310" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E310" s="8" t="n">
-        <v>0</v>
+        <v>190387.81</v>
       </c>
     </row>
     <row r="311">
@@ -6655,13 +6655,13 @@
         </is>
       </c>
       <c r="C311" s="8" t="n">
-        <v>0</v>
+        <v>88402.98</v>
       </c>
       <c r="D311" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E311" s="8" t="n">
-        <v>0</v>
+        <v>88402.98</v>
       </c>
     </row>
     <row r="312">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="C342" s="10" t="n">
-        <v>7298.95</v>
+        <v>1519878.19</v>
       </c>
       <c r="D342" s="10" t="n">
         <v>15513.28</v>
       </c>
       <c r="E342" s="10" t="n">
-        <v>22812.24</v>
+        <v>1535391.48</v>
       </c>
     </row>
     <row r="343">
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="C345" s="10" t="n">
-        <v>7298.95</v>
+        <v>1519878.19</v>
       </c>
       <c r="D345" s="10" t="n">
         <v>15513.28</v>
       </c>
       <c r="E345" s="10" t="n">
-        <v>22812.24</v>
+        <v>1535391.48</v>
       </c>
     </row>
   </sheetData>

--- a/data/informes/cuadro_10_5.xlsx
+++ b/data/informes/cuadro_10_5.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>28230340.21</v>
+        <v>27446870.28</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>110029.6</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>28340369.81</v>
+        <v>27556899.88</v>
       </c>
     </row>
     <row r="6">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>20214769.56</v>
+        <v>19646633.19</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>20214769.56</v>
+        <v>19646633.19</v>
       </c>
     </row>
     <row r="7">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>59509.36</v>
+        <v>36750.72</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>47908.6</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>107417.96</v>
+        <v>84659.32000000001</v>
       </c>
     </row>
     <row r="9">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>3993032.02</v>
+        <v>4016162.67</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>3993032.02</v>
+        <v>4016162.67</v>
       </c>
     </row>
     <row r="10">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1418081.62</v>
+        <v>1202376.05</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1418081.62</v>
+        <v>1202376.05</v>
       </c>
     </row>
     <row r="11">
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>31021821.23</v>
+        <v>30238351.3</v>
       </c>
       <c r="D41" s="10" t="n">
         <v>4022010.07</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>35043831.29</v>
+        <v>34260361.36</v>
       </c>
     </row>
     <row r="42">
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>31021821.23</v>
+        <v>30238351.3</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>4022010.07</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>35043831.29</v>
+        <v>34260361.36</v>
       </c>
     </row>
     <row r="46">
@@ -1402,13 +1402,13 @@
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>29666737.76</v>
+        <v>35392286.66</v>
       </c>
       <c r="D48" s="6" t="n">
         <v>536226.28</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>30202964.04</v>
+        <v>35928512.94</v>
       </c>
     </row>
     <row r="49">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>20629906.84</v>
+        <v>25208602.67</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>20629906.84</v>
+        <v>25208602.67</v>
       </c>
     </row>
     <row r="50">
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>3057447.39</v>
+        <v>3086063.24</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>4801.95</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>3062249.34</v>
+        <v>3090865.19</v>
       </c>
     </row>
     <row r="52">
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>3323709.29</v>
+        <v>3885095.08</v>
       </c>
       <c r="D52" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>3323709.29</v>
+        <v>3885095.08</v>
       </c>
     </row>
     <row r="53">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>2037965.92</v>
+        <v>2594817.35</v>
       </c>
       <c r="D53" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>2037965.92</v>
+        <v>2594817.35</v>
       </c>
     </row>
     <row r="54">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>30306274.39</v>
+        <v>36031823.29</v>
       </c>
       <c r="D84" s="10" t="n">
         <v>2832055.18</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>33138329.57</v>
+        <v>38863878.47</v>
       </c>
     </row>
     <row r="85">
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>30306274.39</v>
+        <v>36031823.29</v>
       </c>
       <c r="D87" s="10" t="n">
         <v>2832055.18</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>33138329.57</v>
+        <v>38863878.47</v>
       </c>
     </row>
     <row r="89">
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="C91" s="6" t="n">
-        <v>17083760.34</v>
+        <v>17710143.89</v>
       </c>
       <c r="D91" s="6" t="n">
         <v>1466749.27</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>18550509.61</v>
+        <v>19176893.16</v>
       </c>
     </row>
     <row r="92">
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>6173152.63</v>
+        <v>6687503.11</v>
       </c>
       <c r="D92" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>6173152.63</v>
+        <v>6687503.11</v>
       </c>
     </row>
     <row r="93">
@@ -2323,13 +2323,13 @@
         </is>
       </c>
       <c r="C94" s="8" t="n">
-        <v>5154366.7</v>
+        <v>5154835.91</v>
       </c>
       <c r="D94" s="8" t="n">
         <v>339568.43</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>5493935.13</v>
+        <v>5494404.34</v>
       </c>
     </row>
     <row r="95">
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>2891873.41</v>
+        <v>2950702.75</v>
       </c>
       <c r="D95" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>2891873.41</v>
+        <v>2950702.75</v>
       </c>
     </row>
     <row r="96">
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>565042.6</v>
+        <v>617777.12</v>
       </c>
       <c r="D96" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>565042.6</v>
+        <v>617777.12</v>
       </c>
     </row>
     <row r="97">
@@ -3012,13 +3012,13 @@
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>19307680.21</v>
+        <v>19934063.76</v>
       </c>
       <c r="D127" s="10" t="n">
         <v>6068958.33</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>25376638.53</v>
+        <v>26003022.08</v>
       </c>
     </row>
     <row r="128">
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>19307680.21</v>
+        <v>19934063.76</v>
       </c>
       <c r="D130" s="10" t="n">
         <v>6068958.33</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>25376638.53</v>
+        <v>26003022.08</v>
       </c>
     </row>
     <row r="132">
@@ -4834,13 +4834,13 @@
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>20735474.68</v>
+        <v>20642223.42</v>
       </c>
       <c r="D220" s="6" t="n">
         <v>279076.91</v>
       </c>
       <c r="E220" s="6" t="n">
-        <v>21014551.59</v>
+        <v>20921300.33</v>
       </c>
     </row>
     <row r="221">
@@ -4855,13 +4855,13 @@
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>1538303.98</v>
+        <v>1458574.68</v>
       </c>
       <c r="D221" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E221" s="8" t="n">
-        <v>1538303.98</v>
+        <v>1458574.68</v>
       </c>
     </row>
     <row r="222">
@@ -4897,13 +4897,13 @@
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>1852184.67</v>
+        <v>1852181.76</v>
       </c>
       <c r="D223" s="8" t="n">
         <v>30144.92</v>
       </c>
       <c r="E223" s="8" t="n">
-        <v>1882329.59</v>
+        <v>1882326.68</v>
       </c>
     </row>
     <row r="224">
@@ -4918,13 +4918,13 @@
         </is>
       </c>
       <c r="C224" s="8" t="n">
-        <v>3884976.34</v>
+        <v>3888592.4</v>
       </c>
       <c r="D224" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E224" s="8" t="n">
-        <v>3884976.34</v>
+        <v>3888592.4</v>
       </c>
     </row>
     <row r="225">
@@ -4939,13 +4939,13 @@
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>181907.55</v>
+        <v>164772.44</v>
       </c>
       <c r="D225" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E225" s="8" t="n">
-        <v>181907.55</v>
+        <v>164772.44</v>
       </c>
     </row>
     <row r="226">
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="C256" s="10" t="n">
-        <v>21698856.19</v>
+        <v>21605604.93</v>
       </c>
       <c r="D256" s="10" t="n">
         <v>11357283.32</v>
       </c>
       <c r="E256" s="10" t="n">
-        <v>33056139.51</v>
+        <v>32962888.25</v>
       </c>
     </row>
     <row r="257">
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="C259" s="10" t="n">
-        <v>21698856.19</v>
+        <v>21605604.93</v>
       </c>
       <c r="D259" s="10" t="n">
         <v>11357283.32</v>
       </c>
       <c r="E259" s="10" t="n">
-        <v>33056139.51</v>
+        <v>32962888.25</v>
       </c>
     </row>
     <row r="261">
@@ -6550,13 +6550,13 @@
         </is>
       </c>
       <c r="C306" s="6" t="n">
-        <v>1512579.24</v>
+        <v>1512579.25</v>
       </c>
       <c r="D306" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E306" s="6" t="n">
-        <v>1512579.24</v>
+        <v>1512579.25</v>
       </c>
     </row>
     <row r="307">
@@ -6655,13 +6655,13 @@
         </is>
       </c>
       <c r="C311" s="8" t="n">
-        <v>88402.98</v>
+        <v>88402.99000000001</v>
       </c>
       <c r="D311" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E311" s="8" t="n">
-        <v>88402.98</v>
+        <v>88402.99000000001</v>
       </c>
     </row>
     <row r="312">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="C342" s="10" t="n">
-        <v>1519878.19</v>
+        <v>1519878.2</v>
       </c>
       <c r="D342" s="10" t="n">
         <v>15513.28</v>
       </c>
       <c r="E342" s="10" t="n">
-        <v>1535391.48</v>
+        <v>1535391.49</v>
       </c>
     </row>
     <row r="343">
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="C345" s="10" t="n">
-        <v>1519878.19</v>
+        <v>1519878.2</v>
       </c>
       <c r="D345" s="10" t="n">
         <v>15513.28</v>
       </c>
       <c r="E345" s="10" t="n">
-        <v>1535391.48</v>
+        <v>1535391.49</v>
       </c>
     </row>
   </sheetData>

--- a/data/informes/cuadro_10_5.xlsx
+++ b/data/informes/cuadro_10_5.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>27446870.28</v>
+        <v>27495286.42</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>110029.6</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>27556899.88</v>
+        <v>27605316.02</v>
       </c>
     </row>
     <row r="6">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>19646633.19</v>
+        <v>19733139.54</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>19646633.19</v>
+        <v>19733139.54</v>
       </c>
     </row>
     <row r="7">
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>2538116.42</v>
+        <v>2408864.3</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>2538116.42</v>
+        <v>2408864.3</v>
       </c>
     </row>
     <row r="8">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>36750.72</v>
+        <v>38426.78</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>47908.6</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>84659.32000000001</v>
+        <v>86335.38</v>
       </c>
     </row>
     <row r="9">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>4016162.67</v>
+        <v>4104709.61</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>4016162.67</v>
+        <v>4104709.61</v>
       </c>
     </row>
     <row r="10">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1202376.05</v>
+        <v>1203314.96</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1202376.05</v>
+        <v>1203314.96</v>
       </c>
     </row>
     <row r="11">
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>30238351.3</v>
+        <v>30286767.44</v>
       </c>
       <c r="D41" s="10" t="n">
         <v>4022010.07</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>34260361.36</v>
+        <v>34308777.5</v>
       </c>
     </row>
     <row r="42">
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>30238351.3</v>
+        <v>30286767.44</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>4022010.07</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>34260361.36</v>
+        <v>34308777.5</v>
       </c>
     </row>
     <row r="46">
@@ -1402,13 +1402,13 @@
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>35392286.66</v>
+        <v>40126098.66</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>536226.28</v>
+        <v>1011649.29</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>35928512.94</v>
+        <v>41137747.95</v>
       </c>
     </row>
     <row r="49">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>25208602.67</v>
+        <v>25880163.45</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>25208602.67</v>
+        <v>25880163.45</v>
       </c>
     </row>
     <row r="50">
@@ -1444,13 +1444,13 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>617658.3199999999</v>
+        <v>616812.63</v>
       </c>
       <c r="D50" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>617658.3199999999</v>
+        <v>616812.63</v>
       </c>
     </row>
     <row r="51">
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>3086063.24</v>
+        <v>6036915.88</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>4801.95</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>3090865.19</v>
+        <v>6041717.83</v>
       </c>
     </row>
     <row r="52">
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>3885095.08</v>
+        <v>4923733.26</v>
       </c>
       <c r="D52" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>3885095.08</v>
+        <v>4923733.26</v>
       </c>
     </row>
     <row r="53">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>2594817.35</v>
+        <v>2668423.44</v>
       </c>
       <c r="D53" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>2594817.35</v>
+        <v>2668423.44</v>
       </c>
     </row>
     <row r="54">
@@ -1552,10 +1552,10 @@
         <v>0</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>98956.25999999999</v>
+        <v>191067.51</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>98956.25999999999</v>
+        <v>191067.51</v>
       </c>
     </row>
     <row r="56">
@@ -1573,10 +1573,10 @@
         <v>0</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>432468.07</v>
+        <v>815779.83</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>432468.07</v>
+        <v>815779.83</v>
       </c>
     </row>
     <row r="57">
@@ -1636,10 +1636,10 @@
         <v>0</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>1163653.69</v>
+        <v>2052394.15</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>1163653.69</v>
+        <v>2052394.15</v>
       </c>
     </row>
     <row r="60">
@@ -1678,10 +1678,10 @@
         <v>0</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>32641.79</v>
+        <v>51304.93</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>32641.79</v>
+        <v>51304.93</v>
       </c>
     </row>
     <row r="62">
@@ -1699,10 +1699,10 @@
         <v>0</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>12418.38</v>
+        <v>73713.44</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>12418.38</v>
+        <v>73713.44</v>
       </c>
     </row>
     <row r="63">
@@ -1720,10 +1720,10 @@
         <v>0</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>552467.51</v>
+        <v>925571.7</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>552467.51</v>
+        <v>925571.7</v>
       </c>
     </row>
     <row r="64">
@@ -1741,10 +1741,10 @@
         <v>0</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>474501.65</v>
+        <v>803974.1800000001</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>474501.65</v>
+        <v>803974.1800000001</v>
       </c>
     </row>
     <row r="65">
@@ -1762,10 +1762,10 @@
         <v>0</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>55388.84</v>
+        <v>156059.26</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>55388.84</v>
+        <v>156059.26</v>
       </c>
     </row>
     <row r="66">
@@ -1783,10 +1783,10 @@
         <v>260827.49</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>988922.62</v>
+        <v>1282108.86</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>1249750.11</v>
+        <v>1542936.35</v>
       </c>
     </row>
     <row r="67">
@@ -1804,10 +1804,10 @@
         <v>0</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>360766.36</v>
+        <v>365866.59</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>360766.36</v>
+        <v>365866.59</v>
       </c>
     </row>
     <row r="68">
@@ -1825,10 +1825,10 @@
         <v>0</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>74535.88</v>
+        <v>158407.34</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>74535.88</v>
+        <v>158407.34</v>
       </c>
     </row>
     <row r="69">
@@ -1846,10 +1846,10 @@
         <v>260827.49</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>55018.35</v>
+        <v>102086.06</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>315845.84</v>
+        <v>362913.55</v>
       </c>
     </row>
     <row r="70">
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>177292</v>
+        <v>251450.86</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>177292</v>
+        <v>251450.86</v>
       </c>
     </row>
     <row r="74">
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>306.46</v>
+        <v>379.72</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>306.46</v>
+        <v>379.72</v>
       </c>
     </row>
     <row r="75">
@@ -2077,10 +2077,10 @@
         <v>0</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>142870.05</v>
+        <v>196207.84</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>142870.05</v>
+        <v>196207.84</v>
       </c>
     </row>
     <row r="81">
@@ -2098,10 +2098,10 @@
         <v>0</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>138370.05</v>
+        <v>191707.84</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>138370.05</v>
+        <v>191707.84</v>
       </c>
     </row>
     <row r="82">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>36031823.29</v>
+        <v>40765635.29</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>2832055.18</v>
+        <v>4542815.94</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>38863878.47</v>
+        <v>45308451.23</v>
       </c>
     </row>
     <row r="85">
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>36031823.29</v>
+        <v>40765635.29</v>
       </c>
       <c r="D87" s="10" t="n">
-        <v>2832055.18</v>
+        <v>4542815.94</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>38863878.47</v>
+        <v>45308451.23</v>
       </c>
     </row>
     <row r="89">
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="C91" s="6" t="n">
-        <v>17710143.89</v>
+        <v>12685035.35</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>1466749.27</v>
+        <v>991326.26</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>19176893.16</v>
+        <v>13676361.61</v>
       </c>
     </row>
     <row r="92">
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>6687503.11</v>
+        <v>5849601.49</v>
       </c>
       <c r="D92" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>6687503.11</v>
+        <v>5849601.49</v>
       </c>
     </row>
     <row r="93">
@@ -2302,13 +2302,13 @@
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>2047253.51</v>
+        <v>1946411.86</v>
       </c>
       <c r="D93" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>2047253.51</v>
+        <v>1946411.86</v>
       </c>
     </row>
     <row r="94">
@@ -2323,13 +2323,13 @@
         </is>
       </c>
       <c r="C94" s="8" t="n">
-        <v>5154835.91</v>
+        <v>2153526.95</v>
       </c>
       <c r="D94" s="8" t="n">
         <v>339568.43</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>5494404.34</v>
+        <v>2493095.38</v>
       </c>
     </row>
     <row r="95">
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>2950702.75</v>
+        <v>1936585.56</v>
       </c>
       <c r="D95" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>2950702.75</v>
+        <v>1936585.56</v>
       </c>
     </row>
     <row r="96">
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>617777.12</v>
+        <v>546838</v>
       </c>
       <c r="D96" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>617777.12</v>
+        <v>546838</v>
       </c>
     </row>
     <row r="97">
@@ -2410,10 +2410,10 @@
         <v>0</v>
       </c>
       <c r="D98" s="8" t="n">
-        <v>257717.69</v>
+        <v>165606.44</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>257717.69</v>
+        <v>165606.44</v>
       </c>
     </row>
     <row r="99">
@@ -2431,10 +2431,10 @@
         <v>0</v>
       </c>
       <c r="D99" s="8" t="n">
-        <v>869463.15</v>
+        <v>486151.39</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>869463.15</v>
+        <v>486151.39</v>
       </c>
     </row>
     <row r="100">
@@ -2494,10 +2494,10 @@
         <v>0</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>2082204.86</v>
+        <v>1193464.4</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>2082204.86</v>
+        <v>1193464.4</v>
       </c>
     </row>
     <row r="103">
@@ -2536,10 +2536,10 @@
         <v>0</v>
       </c>
       <c r="D104" s="8" t="n">
-        <v>137057.68</v>
+        <v>118394.54</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>137057.68</v>
+        <v>118394.54</v>
       </c>
     </row>
     <row r="105">
@@ -2557,10 +2557,10 @@
         <v>0</v>
       </c>
       <c r="D105" s="8" t="n">
-        <v>93365.2</v>
+        <v>32070.14</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>93365.2</v>
+        <v>32070.14</v>
       </c>
     </row>
     <row r="106">
@@ -2578,10 +2578,10 @@
         <v>0</v>
       </c>
       <c r="D106" s="8" t="n">
-        <v>617414.9</v>
+        <v>244310.71</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>617414.9</v>
+        <v>244310.71</v>
       </c>
     </row>
     <row r="107">
@@ -2599,10 +2599,10 @@
         <v>0</v>
       </c>
       <c r="D107" s="8" t="n">
-        <v>862765</v>
+        <v>533292.47</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>862765</v>
+        <v>533292.47</v>
       </c>
     </row>
     <row r="108">
@@ -2620,10 +2620,10 @@
         <v>0</v>
       </c>
       <c r="D108" s="8" t="n">
-        <v>196587.77</v>
+        <v>95917.35000000001</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>196587.77</v>
+        <v>95917.35000000001</v>
       </c>
     </row>
     <row r="109">
@@ -2641,10 +2641,10 @@
         <v>406473.49</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>2329006.45</v>
+        <v>2035820.21</v>
       </c>
       <c r="E109" s="6" t="n">
-        <v>2735479.93</v>
+        <v>2442293.69</v>
       </c>
     </row>
     <row r="110">
@@ -2662,10 +2662,10 @@
         <v>0</v>
       </c>
       <c r="D110" s="8" t="n">
-        <v>801374.3100000001</v>
+        <v>796274.08</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>801374.3100000001</v>
+        <v>796274.08</v>
       </c>
     </row>
     <row r="111">
@@ -2683,10 +2683,10 @@
         <v>0</v>
       </c>
       <c r="D111" s="8" t="n">
-        <v>222473.18</v>
+        <v>138601.72</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>222473.18</v>
+        <v>138601.72</v>
       </c>
     </row>
     <row r="112">
@@ -2704,10 +2704,10 @@
         <v>406473.49</v>
       </c>
       <c r="D112" s="8" t="n">
-        <v>103857.66</v>
+        <v>56789.95</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>510331.15</v>
+        <v>463263.44</v>
       </c>
     </row>
     <row r="113">
@@ -2788,10 +2788,10 @@
         <v>0</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>292736.43</v>
+        <v>218577.57</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>292736.43</v>
+        <v>218577.57</v>
       </c>
     </row>
     <row r="117">
@@ -2809,10 +2809,10 @@
         <v>0</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>444.81</v>
+        <v>371.55</v>
       </c>
       <c r="E117" s="6" t="n">
-        <v>444.81</v>
+        <v>371.55</v>
       </c>
     </row>
     <row r="118">
@@ -2935,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>190552.94</v>
+        <v>137215.15</v>
       </c>
       <c r="E123" s="6" t="n">
-        <v>190552.94</v>
+        <v>137215.15</v>
       </c>
     </row>
     <row r="124">
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="D124" s="8" t="n">
-        <v>190552.94</v>
+        <v>137215.15</v>
       </c>
       <c r="E124" s="8" t="n">
-        <v>190552.94</v>
+        <v>137215.15</v>
       </c>
     </row>
     <row r="125">
@@ -3012,13 +3012,13 @@
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>19934063.76</v>
+        <v>14908955.22</v>
       </c>
       <c r="D127" s="10" t="n">
-        <v>6068958.33</v>
+        <v>4358197.57</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>26003022.08</v>
+        <v>19267152.78</v>
       </c>
     </row>
     <row r="128">
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>19934063.76</v>
+        <v>14908955.22</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>6068958.33</v>
+        <v>4358197.57</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>26003022.08</v>
+        <v>19267152.78</v>
       </c>
     </row>
     <row r="132">
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>8507962.880000001</v>
+        <v>8154049.13</v>
       </c>
       <c r="D134" s="6" t="n">
         <v>45763.01</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>8553725.890000001</v>
+        <v>8199812.14</v>
       </c>
     </row>
     <row r="135">
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>102384.33</v>
+        <v>102638.2</v>
       </c>
       <c r="D135" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>102384.33</v>
+        <v>102638.2</v>
       </c>
     </row>
     <row r="136">
@@ -3160,13 +3160,13 @@
         </is>
       </c>
       <c r="C136" s="8" t="n">
-        <v>6668990.07</v>
+        <v>6310448.47</v>
       </c>
       <c r="D136" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E136" s="8" t="n">
-        <v>6668990.07</v>
+        <v>6310448.47</v>
       </c>
     </row>
     <row r="137">
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="C138" s="8" t="n">
-        <v>1676782.82</v>
+        <v>1681118.53</v>
       </c>
       <c r="D138" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E138" s="8" t="n">
-        <v>1676782.82</v>
+        <v>1681118.53</v>
       </c>
     </row>
     <row r="139">
@@ -3223,13 +3223,13 @@
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>7905.21</v>
+        <v>7943.48</v>
       </c>
       <c r="D139" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>7905.21</v>
+        <v>7943.48</v>
       </c>
     </row>
     <row r="140">
@@ -3870,13 +3870,13 @@
         </is>
       </c>
       <c r="C170" s="10" t="n">
-        <v>9399639.83</v>
+        <v>9045726.08</v>
       </c>
       <c r="D170" s="10" t="n">
         <v>1496714.99</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>10896354.82</v>
+        <v>10542441.06</v>
       </c>
     </row>
     <row r="171">
@@ -3921,13 +3921,13 @@
         </is>
       </c>
       <c r="C173" s="10" t="n">
-        <v>9399639.83</v>
+        <v>9045726.08</v>
       </c>
       <c r="D173" s="10" t="n">
         <v>1496714.99</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>10896354.82</v>
+        <v>10542441.06</v>
       </c>
     </row>
     <row r="175">
@@ -3976,13 +3976,13 @@
         </is>
       </c>
       <c r="C177" s="6" t="n">
-        <v>2327149.81</v>
+        <v>2266836.5</v>
       </c>
       <c r="D177" s="6" t="n">
         <v>24069.71</v>
       </c>
       <c r="E177" s="6" t="n">
-        <v>2351219.52</v>
+        <v>2290906.21</v>
       </c>
     </row>
     <row r="178">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>1797367.91</v>
+        <v>1736105.83</v>
       </c>
       <c r="D179" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E179" s="8" t="n">
-        <v>1797367.91</v>
+        <v>1736105.83</v>
       </c>
     </row>
     <row r="180">
@@ -4060,13 +4060,13 @@
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>478830.19</v>
+        <v>479778.95</v>
       </c>
       <c r="D181" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E181" s="8" t="n">
-        <v>478830.19</v>
+        <v>479778.95</v>
       </c>
     </row>
     <row r="182">
@@ -4728,13 +4728,13 @@
         </is>
       </c>
       <c r="C213" s="10" t="n">
-        <v>3068035.19</v>
+        <v>3007721.87</v>
       </c>
       <c r="D213" s="10" t="n">
         <v>2082891.57</v>
       </c>
       <c r="E213" s="10" t="n">
-        <v>5150926.76</v>
+        <v>5090613.44</v>
       </c>
     </row>
     <row r="214">
@@ -4779,13 +4779,13 @@
         </is>
       </c>
       <c r="C216" s="10" t="n">
-        <v>3068035.19</v>
+        <v>3007721.87</v>
       </c>
       <c r="D216" s="10" t="n">
         <v>2082891.57</v>
       </c>
       <c r="E216" s="10" t="n">
-        <v>5150926.76</v>
+        <v>5090613.44</v>
       </c>
     </row>
     <row r="218">
@@ -4834,13 +4834,13 @@
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>20642223.42</v>
+        <v>20173416.44</v>
       </c>
       <c r="D220" s="6" t="n">
         <v>279076.91</v>
       </c>
       <c r="E220" s="6" t="n">
-        <v>20921300.33</v>
+        <v>20452493.35</v>
       </c>
     </row>
     <row r="221">
@@ -4855,13 +4855,13 @@
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>1458574.68</v>
+        <v>1473887.3</v>
       </c>
       <c r="D221" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E221" s="8" t="n">
-        <v>1458574.68</v>
+        <v>1473887.3</v>
       </c>
     </row>
     <row r="222">
@@ -4876,13 +4876,13 @@
         </is>
       </c>
       <c r="C222" s="8" t="n">
-        <v>13245948</v>
+        <v>12741181.36</v>
       </c>
       <c r="D222" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E222" s="8" t="n">
-        <v>13245948</v>
+        <v>12741181.36</v>
       </c>
     </row>
     <row r="223">
@@ -4897,13 +4897,13 @@
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>1852181.76</v>
+        <v>1872797.11</v>
       </c>
       <c r="D223" s="8" t="n">
         <v>30144.92</v>
       </c>
       <c r="E223" s="8" t="n">
-        <v>1882326.68</v>
+        <v>1902942.03</v>
       </c>
     </row>
     <row r="224">
@@ -4918,13 +4918,13 @@
         </is>
       </c>
       <c r="C224" s="8" t="n">
-        <v>3888592.4</v>
+        <v>3888558.43</v>
       </c>
       <c r="D224" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E224" s="8" t="n">
-        <v>3888592.4</v>
+        <v>3888558.43</v>
       </c>
     </row>
     <row r="225">
@@ -4939,13 +4939,13 @@
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>164772.44</v>
+        <v>164838.09</v>
       </c>
       <c r="D225" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E225" s="8" t="n">
-        <v>164772.44</v>
+        <v>164838.09</v>
       </c>
     </row>
     <row r="226">
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="C256" s="10" t="n">
-        <v>21605604.93</v>
+        <v>21136797.94</v>
       </c>
       <c r="D256" s="10" t="n">
         <v>11357283.32</v>
       </c>
       <c r="E256" s="10" t="n">
-        <v>32962888.25</v>
+        <v>32494081.27</v>
       </c>
     </row>
     <row r="257">
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="C259" s="10" t="n">
-        <v>21605604.93</v>
+        <v>21136797.94</v>
       </c>
       <c r="D259" s="10" t="n">
         <v>11357283.32</v>
       </c>
       <c r="E259" s="10" t="n">
-        <v>32962888.25</v>
+        <v>32494081.27</v>
       </c>
     </row>
     <row r="261">
@@ -6550,13 +6550,13 @@
         </is>
       </c>
       <c r="C306" s="6" t="n">
-        <v>1512579.25</v>
+        <v>1508929.53</v>
       </c>
       <c r="D306" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E306" s="6" t="n">
-        <v>1512579.25</v>
+        <v>1508929.53</v>
       </c>
     </row>
     <row r="307">
@@ -6571,13 +6571,13 @@
         </is>
       </c>
       <c r="C307" s="8" t="n">
-        <v>897414</v>
+        <v>896382.46</v>
       </c>
       <c r="D307" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E307" s="8" t="n">
-        <v>897414</v>
+        <v>896382.46</v>
       </c>
     </row>
     <row r="308">
@@ -6592,13 +6592,13 @@
         </is>
       </c>
       <c r="C308" s="8" t="n">
-        <v>336374.45</v>
+        <v>333761.33</v>
       </c>
       <c r="D308" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E308" s="8" t="n">
-        <v>336374.45</v>
+        <v>333761.33</v>
       </c>
     </row>
     <row r="309">
@@ -6634,13 +6634,13 @@
         </is>
       </c>
       <c r="C310" s="8" t="n">
-        <v>190387.81</v>
+        <v>190382.76</v>
       </c>
       <c r="D310" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E310" s="8" t="n">
-        <v>190387.81</v>
+        <v>190382.76</v>
       </c>
     </row>
     <row r="311">
@@ -6655,13 +6655,13 @@
         </is>
       </c>
       <c r="C311" s="8" t="n">
-        <v>88402.99000000001</v>
+        <v>88402.97</v>
       </c>
       <c r="D311" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E311" s="8" t="n">
-        <v>88402.99000000001</v>
+        <v>88402.97</v>
       </c>
     </row>
     <row r="312">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="C342" s="10" t="n">
-        <v>1519878.2</v>
+        <v>1516228.48</v>
       </c>
       <c r="D342" s="10" t="n">
         <v>15513.28</v>
       </c>
       <c r="E342" s="10" t="n">
-        <v>1535391.49</v>
+        <v>1531741.76</v>
       </c>
     </row>
     <row r="343">
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="C345" s="10" t="n">
-        <v>1519878.2</v>
+        <v>1516228.48</v>
       </c>
       <c r="D345" s="10" t="n">
         <v>15513.28</v>
       </c>
       <c r="E345" s="10" t="n">
-        <v>1535391.49</v>
+        <v>1531741.76</v>
       </c>
     </row>
   </sheetData>

--- a/data/informes/cuadro_10_5.xlsx
+++ b/data/informes/cuadro_10_5.xlsx
@@ -547,10 +547,10 @@
         <v>27495286.42</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>110029.6</v>
+        <v>107371.84</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>27605316.02</v>
+        <v>27602658.26</v>
       </c>
     </row>
     <row r="6">
@@ -715,10 +715,10 @@
         <v>0</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>56326.22</v>
+        <v>53668.46</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>56326.22</v>
+        <v>53668.46</v>
       </c>
     </row>
     <row r="14">
@@ -778,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>485157.65</v>
+        <v>452240.04</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>485157.65</v>
+        <v>452240.04</v>
       </c>
     </row>
     <row r="17">
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>400693.8</v>
+        <v>367888.19</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>400693.8</v>
+        <v>367888.19</v>
       </c>
     </row>
     <row r="22">
@@ -904,10 +904,10 @@
         <v>0</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>12341.23</v>
+        <v>12229.23</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>12341.23</v>
+        <v>12229.23</v>
       </c>
     </row>
     <row r="23">
@@ -925,10 +925,10 @@
         <v>688443.99</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3323976.44</v>
+        <v>3285385.21</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4012420.43</v>
+        <v>3973829.2</v>
       </c>
     </row>
     <row r="24">
@@ -1072,10 +1072,10 @@
         <v>0</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>99932.2</v>
+        <v>62145.97</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>99932.2</v>
+        <v>62145.97</v>
       </c>
     </row>
     <row r="31">
@@ -1299,10 +1299,10 @@
         <v>30286767.44</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>4022010.07</v>
+        <v>3947843.47</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>34308777.5</v>
+        <v>34234610.9</v>
       </c>
     </row>
     <row r="42">
@@ -1350,10 +1350,10 @@
         <v>30286767.44</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>4022010.07</v>
+        <v>3947843.47</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>34308777.5</v>
+        <v>34234610.9</v>
       </c>
     </row>
     <row r="46">
@@ -1405,10 +1405,10 @@
         <v>40126098.66</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>1011649.29</v>
+        <v>1011396.15</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>41137747.95</v>
+        <v>41137494.81</v>
       </c>
     </row>
     <row r="49">
@@ -1573,10 +1573,10 @@
         <v>0</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>815779.83</v>
+        <v>815526.6899999999</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>815779.83</v>
+        <v>815526.6899999999</v>
       </c>
     </row>
     <row r="57">
@@ -1636,10 +1636,10 @@
         <v>0</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>2052394.15</v>
+        <v>2052265.65</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>2052394.15</v>
+        <v>2052265.65</v>
       </c>
     </row>
     <row r="60">
@@ -1741,10 +1741,10 @@
         <v>0</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>803974.1800000001</v>
+        <v>803845.6800000001</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>803974.1800000001</v>
+        <v>803845.6800000001</v>
       </c>
     </row>
     <row r="65">
@@ -1780,13 +1780,13 @@
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>260827.49</v>
+        <v>259941.34</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>1282108.86</v>
+        <v>1277308.65</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>1542936.35</v>
+        <v>1537249.99</v>
       </c>
     </row>
     <row r="67">
@@ -1804,10 +1804,10 @@
         <v>0</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>365866.59</v>
+        <v>363438.18</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>365866.59</v>
+        <v>363438.18</v>
       </c>
     </row>
     <row r="68">
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>260827.49</v>
+        <v>259941.34</v>
       </c>
       <c r="D69" s="8" t="n">
         <v>102086.06</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>362913.55</v>
+        <v>362027.4</v>
       </c>
     </row>
     <row r="70">
@@ -1888,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>156509.79</v>
+        <v>154818.87</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>156509.79</v>
+        <v>154818.87</v>
       </c>
     </row>
     <row r="72">
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>63021.76</v>
+        <v>62340.88</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>63021.76</v>
+        <v>62340.88</v>
       </c>
     </row>
     <row r="73">
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>378709.13</v>
+        <v>377901.49</v>
       </c>
       <c r="D76" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>378709.13</v>
+        <v>377901.49</v>
       </c>
     </row>
     <row r="77">
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>378709.13</v>
+        <v>377901.49</v>
       </c>
       <c r="D77" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>378709.13</v>
+        <v>377901.49</v>
       </c>
     </row>
     <row r="78">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>40765635.29</v>
+        <v>40763941.5</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>4542815.94</v>
+        <v>4537634.09</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>45308451.23</v>
+        <v>45301575.59</v>
       </c>
     </row>
     <row r="85">
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>40765635.29</v>
+        <v>40763941.5</v>
       </c>
       <c r="D87" s="10" t="n">
-        <v>4542815.94</v>
+        <v>4537634.09</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>45308451.23</v>
+        <v>45301575.59</v>
       </c>
     </row>
     <row r="89">
@@ -2263,10 +2263,10 @@
         <v>12685035.35</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>991326.26</v>
+        <v>994237.16</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>13676361.61</v>
+        <v>13679272.51</v>
       </c>
     </row>
     <row r="92">
@@ -2431,10 +2431,10 @@
         <v>0</v>
       </c>
       <c r="D99" s="8" t="n">
-        <v>486151.39</v>
+        <v>489062.29</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>486151.39</v>
+        <v>489062.29</v>
       </c>
     </row>
     <row r="100">
@@ -2494,10 +2494,10 @@
         <v>0</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>1193464.4</v>
+        <v>1226510.51</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>1193464.4</v>
+        <v>1226510.51</v>
       </c>
     </row>
     <row r="103">
@@ -2599,10 +2599,10 @@
         <v>0</v>
       </c>
       <c r="D107" s="8" t="n">
-        <v>533292.47</v>
+        <v>566226.58</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>533292.47</v>
+        <v>566226.58</v>
       </c>
     </row>
     <row r="108">
@@ -2620,10 +2620,10 @@
         <v>0</v>
       </c>
       <c r="D108" s="8" t="n">
-        <v>95917.35000000001</v>
+        <v>96029.35000000001</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>95917.35000000001</v>
+        <v>96029.35000000001</v>
       </c>
     </row>
     <row r="109">
@@ -2641,10 +2641,10 @@
         <v>406473.49</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>2035820.21</v>
+        <v>2074411.44</v>
       </c>
       <c r="E109" s="6" t="n">
-        <v>2442293.69</v>
+        <v>2480884.92</v>
       </c>
     </row>
     <row r="110">
@@ -2788,10 +2788,10 @@
         <v>0</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>218577.57</v>
+        <v>256363.8</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>218577.57</v>
+        <v>256363.8</v>
       </c>
     </row>
     <row r="117">
@@ -3015,10 +3015,10 @@
         <v>14908955.22</v>
       </c>
       <c r="D127" s="10" t="n">
-        <v>4358197.57</v>
+        <v>4432745.81</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>19267152.78</v>
+        <v>19341701.02</v>
       </c>
     </row>
     <row r="128">
@@ -3066,10 +3066,10 @@
         <v>14908955.22</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>4358197.57</v>
+        <v>4432745.81</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>19267152.78</v>
+        <v>19341701.02</v>
       </c>
     </row>
     <row r="132">
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>8154049.13</v>
+        <v>9234657.890000001</v>
       </c>
       <c r="D134" s="6" t="n">
         <v>45763.01</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>8199812.14</v>
+        <v>9280420.9</v>
       </c>
     </row>
     <row r="135">
@@ -3160,13 +3160,13 @@
         </is>
       </c>
       <c r="C136" s="8" t="n">
-        <v>6310448.47</v>
+        <v>7157914.42</v>
       </c>
       <c r="D136" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E136" s="8" t="n">
-        <v>6310448.47</v>
+        <v>7157914.42</v>
       </c>
     </row>
     <row r="137">
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="C138" s="8" t="n">
-        <v>1681118.53</v>
+        <v>1911645.17</v>
       </c>
       <c r="D138" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E138" s="8" t="n">
-        <v>1681118.53</v>
+        <v>1911645.17</v>
       </c>
     </row>
     <row r="139">
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>3394.46</v>
+        <v>6010.64</v>
       </c>
       <c r="D143" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>3394.46</v>
+        <v>6010.64</v>
       </c>
     </row>
     <row r="144">
@@ -3496,13 +3496,13 @@
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>362068.42</v>
+        <v>366345.7</v>
       </c>
       <c r="D152" s="6" t="n">
-        <v>944906.87</v>
+        <v>959655.9300000001</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>1306975.29</v>
+        <v>1326001.63</v>
       </c>
     </row>
     <row r="153">
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="D153" s="8" t="n">
-        <v>448707.64</v>
+        <v>456169.14</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>448707.64</v>
+        <v>456169.14</v>
       </c>
     </row>
     <row r="154">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>362068.42</v>
+        <v>366345.7</v>
       </c>
       <c r="D155" s="8" t="n">
         <v>12928.13</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>374996.55</v>
+        <v>379273.83</v>
       </c>
     </row>
     <row r="156">
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="D157" s="8" t="n">
-        <v>284800.41</v>
+        <v>289995.9</v>
       </c>
       <c r="E157" s="8" t="n">
-        <v>284800.41</v>
+        <v>289995.9</v>
       </c>
     </row>
     <row r="158">
@@ -3625,10 +3625,10 @@
         <v>0</v>
       </c>
       <c r="D158" s="8" t="n">
-        <v>97087.92</v>
+        <v>99179.99000000001</v>
       </c>
       <c r="E158" s="8" t="n">
-        <v>97087.92</v>
+        <v>99179.99000000001</v>
       </c>
     </row>
     <row r="159">
@@ -3706,13 +3706,13 @@
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>529608.53</v>
+        <v>535820.02</v>
       </c>
       <c r="D162" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E162" s="6" t="n">
-        <v>529608.53</v>
+        <v>535820.02</v>
       </c>
     </row>
     <row r="163">
@@ -3727,13 +3727,13 @@
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>529608.53</v>
+        <v>535820.02</v>
       </c>
       <c r="D163" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E163" s="8" t="n">
-        <v>529608.53</v>
+        <v>535820.02</v>
       </c>
     </row>
     <row r="164">
@@ -3870,13 +3870,13 @@
         </is>
       </c>
       <c r="C170" s="10" t="n">
-        <v>9045726.08</v>
+        <v>10136823.61</v>
       </c>
       <c r="D170" s="10" t="n">
-        <v>1496714.99</v>
+        <v>1511464.05</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>10542441.06</v>
+        <v>11648287.66</v>
       </c>
     </row>
     <row r="171">
@@ -3921,13 +3921,13 @@
         </is>
       </c>
       <c r="C173" s="10" t="n">
-        <v>9045726.08</v>
+        <v>10136823.61</v>
       </c>
       <c r="D173" s="10" t="n">
-        <v>1496714.99</v>
+        <v>1511464.05</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>10542441.06</v>
+        <v>11648287.66</v>
       </c>
     </row>
     <row r="175">
@@ -4834,13 +4834,13 @@
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>20173416.44</v>
+        <v>19092807.67</v>
       </c>
       <c r="D220" s="6" t="n">
         <v>279076.91</v>
       </c>
       <c r="E220" s="6" t="n">
-        <v>20452493.35</v>
+        <v>19371884.58</v>
       </c>
     </row>
     <row r="221">
@@ -4876,13 +4876,13 @@
         </is>
       </c>
       <c r="C222" s="8" t="n">
-        <v>12741181.36</v>
+        <v>11893715.42</v>
       </c>
       <c r="D222" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E222" s="8" t="n">
-        <v>12741181.36</v>
+        <v>11893715.42</v>
       </c>
     </row>
     <row r="223">
@@ -4918,13 +4918,13 @@
         </is>
       </c>
       <c r="C224" s="8" t="n">
-        <v>3888558.43</v>
+        <v>3658031.79</v>
       </c>
       <c r="D224" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E224" s="8" t="n">
-        <v>3888558.43</v>
+        <v>3658031.79</v>
       </c>
     </row>
     <row r="225">
@@ -5023,13 +5023,13 @@
         </is>
       </c>
       <c r="C229" s="8" t="n">
-        <v>32154.14</v>
+        <v>29537.96</v>
       </c>
       <c r="D229" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E229" s="8" t="n">
-        <v>32154.14</v>
+        <v>29537.96</v>
       </c>
     </row>
     <row r="230">
@@ -5212,13 +5212,13 @@
         </is>
       </c>
       <c r="C238" s="6" t="n">
-        <v>309295.54</v>
+        <v>305904.41</v>
       </c>
       <c r="D238" s="6" t="n">
-        <v>3288407.68</v>
+        <v>3278458.83</v>
       </c>
       <c r="E238" s="6" t="n">
-        <v>3597703.22</v>
+        <v>3584363.24</v>
       </c>
     </row>
     <row r="239">
@@ -5236,10 +5236,10 @@
         <v>0</v>
       </c>
       <c r="D239" s="8" t="n">
-        <v>813106.99</v>
+        <v>808073.89</v>
       </c>
       <c r="E239" s="8" t="n">
-        <v>813106.99</v>
+        <v>808073.89</v>
       </c>
     </row>
     <row r="240">
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="C241" s="8" t="n">
-        <v>309295.54</v>
+        <v>305904.41</v>
       </c>
       <c r="D241" s="8" t="n">
         <v>187427.05</v>
       </c>
       <c r="E241" s="8" t="n">
-        <v>496722.59</v>
+        <v>493331.46</v>
       </c>
     </row>
     <row r="242">
@@ -5320,10 +5320,10 @@
         <v>0</v>
       </c>
       <c r="D243" s="8" t="n">
-        <v>308472.19</v>
+        <v>304967.62</v>
       </c>
       <c r="E243" s="8" t="n">
-        <v>308472.19</v>
+        <v>304967.62</v>
       </c>
     </row>
     <row r="244">
@@ -5341,10 +5341,10 @@
         <v>0</v>
       </c>
       <c r="D244" s="8" t="n">
-        <v>124212.43</v>
+        <v>122801.24</v>
       </c>
       <c r="E244" s="8" t="n">
-        <v>124212.43</v>
+        <v>122801.24</v>
       </c>
     </row>
     <row r="245">
@@ -5422,13 +5422,13 @@
         </is>
       </c>
       <c r="C248" s="6" t="n">
-        <v>654085.97</v>
+        <v>648682.12</v>
       </c>
       <c r="D248" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E248" s="6" t="n">
-        <v>654085.97</v>
+        <v>648682.12</v>
       </c>
     </row>
     <row r="249">
@@ -5443,13 +5443,13 @@
         </is>
       </c>
       <c r="C249" s="8" t="n">
-        <v>654085.97</v>
+        <v>648682.12</v>
       </c>
       <c r="D249" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E249" s="8" t="n">
-        <v>654085.97</v>
+        <v>648682.12</v>
       </c>
     </row>
     <row r="250">
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="C256" s="10" t="n">
-        <v>21136797.94</v>
+        <v>20047394.21</v>
       </c>
       <c r="D256" s="10" t="n">
-        <v>11357283.32</v>
+        <v>11347334.47</v>
       </c>
       <c r="E256" s="10" t="n">
-        <v>32494081.27</v>
+        <v>31394728.67</v>
       </c>
     </row>
     <row r="257">
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="C259" s="10" t="n">
-        <v>21136797.94</v>
+        <v>20047394.21</v>
       </c>
       <c r="D259" s="10" t="n">
-        <v>11357283.32</v>
+        <v>11347334.47</v>
       </c>
       <c r="E259" s="10" t="n">
-        <v>32494081.27</v>
+        <v>31394728.67</v>
       </c>
     </row>
     <row r="261">

--- a/data/informes/cuadro_10_5.xlsx
+++ b/data/informes/cuadro_10_5.xlsx
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>688443.99</v>
+        <v>698845.48</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3285385.21</v>
+        <v>3375187.01</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>3973829.2</v>
+        <v>4074032.49</v>
       </c>
     </row>
     <row r="24">
@@ -946,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1565485.25</v>
+        <v>1610915.7</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>1565485.25</v>
+        <v>1610915.7</v>
       </c>
     </row>
     <row r="25">
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>688443.99</v>
+        <v>698845.48</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>688443.99</v>
+        <v>698845.48</v>
       </c>
     </row>
     <row r="27">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>1089395.77</v>
+        <v>1121029.27</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>1089395.77</v>
+        <v>1121029.27</v>
       </c>
     </row>
     <row r="29">
@@ -1051,10 +1051,10 @@
         <v>0</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>438666.76</v>
+        <v>451404.61</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>438666.76</v>
+        <v>451404.61</v>
       </c>
     </row>
     <row r="30">
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>30286767.44</v>
+        <v>30297168.92</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>3947843.47</v>
+        <v>4037645.27</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>34234610.9</v>
+        <v>34334814.19</v>
       </c>
     </row>
     <row r="42">
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>30286767.44</v>
+        <v>30297168.92</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>3947843.47</v>
+        <v>4037645.27</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>34234610.9</v>
+        <v>34334814.19</v>
       </c>
     </row>
     <row r="46">
@@ -1780,13 +1780,13 @@
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>259941.34</v>
+        <v>259973.61</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>1277308.65</v>
+        <v>1277200.75</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>1537249.99</v>
+        <v>1537174.35</v>
       </c>
     </row>
     <row r="67">
@@ -1804,10 +1804,10 @@
         <v>0</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>363438.18</v>
+        <v>363383.59</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>363438.18</v>
+        <v>363383.59</v>
       </c>
     </row>
     <row r="68">
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>259941.34</v>
+        <v>259973.61</v>
       </c>
       <c r="D69" s="8" t="n">
         <v>102086.06</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>362027.4</v>
+        <v>362059.67</v>
       </c>
     </row>
     <row r="70">
@@ -1888,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>154818.87</v>
+        <v>154780.86</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>154818.87</v>
+        <v>154780.86</v>
       </c>
     </row>
     <row r="72">
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>62340.88</v>
+        <v>62325.58</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>62340.88</v>
+        <v>62325.58</v>
       </c>
     </row>
     <row r="73">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>40763941.5</v>
+        <v>40763973.76</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>4537634.09</v>
+        <v>4537526.19</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>45301575.59</v>
+        <v>45301499.95</v>
       </c>
     </row>
     <row r="85">
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>40763941.5</v>
+        <v>40763973.76</v>
       </c>
       <c r="D87" s="10" t="n">
-        <v>4537634.09</v>
+        <v>4537526.19</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>45301575.59</v>
+        <v>45301499.95</v>
       </c>
     </row>
     <row r="89">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="C109" s="6" t="n">
-        <v>406473.49</v>
+        <v>391663.59</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>2074411.44</v>
+        <v>1956198.23</v>
       </c>
       <c r="E109" s="6" t="n">
-        <v>2480884.92</v>
+        <v>2347861.82</v>
       </c>
     </row>
     <row r="110">
@@ -2662,10 +2662,10 @@
         <v>0</v>
       </c>
       <c r="D110" s="8" t="n">
-        <v>796274.08</v>
+        <v>736470.39</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>796274.08</v>
+        <v>736470.39</v>
       </c>
     </row>
     <row r="111">
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="C112" s="8" t="n">
-        <v>406473.49</v>
+        <v>391663.59</v>
       </c>
       <c r="D112" s="8" t="n">
         <v>56789.95</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>463263.44</v>
+        <v>448453.54</v>
       </c>
     </row>
     <row r="113">
@@ -2746,10 +2746,10 @@
         <v>0</v>
       </c>
       <c r="D114" s="8" t="n">
-        <v>502160.84</v>
+        <v>460519.16</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>502160.84</v>
+        <v>460519.16</v>
       </c>
     </row>
     <row r="115">
@@ -2767,10 +2767,10 @@
         <v>0</v>
       </c>
       <c r="D115" s="8" t="n">
-        <v>202204.99</v>
+        <v>185437.15</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>202204.99</v>
+        <v>185437.15</v>
       </c>
     </row>
     <row r="116">
@@ -3012,13 +3012,13 @@
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>14908955.22</v>
+        <v>14894145.32</v>
       </c>
       <c r="D127" s="10" t="n">
-        <v>4432745.81</v>
+        <v>4314532.6</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>19341701.02</v>
+        <v>19208677.92</v>
       </c>
     </row>
     <row r="128">
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>14908955.22</v>
+        <v>14894145.32</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>4432745.81</v>
+        <v>4314532.6</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>19341701.02</v>
+        <v>19208677.92</v>
       </c>
     </row>
     <row r="132">
@@ -3496,13 +3496,13 @@
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>366345.7</v>
+        <v>364702.58</v>
       </c>
       <c r="D152" s="6" t="n">
         <v>959655.9300000001</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>1326001.63</v>
+        <v>1324358.52</v>
       </c>
     </row>
     <row r="153">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>366345.7</v>
+        <v>364702.58</v>
       </c>
       <c r="D155" s="8" t="n">
         <v>12928.13</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>379273.83</v>
+        <v>377630.71</v>
       </c>
     </row>
     <row r="156">
@@ -3870,13 +3870,13 @@
         </is>
       </c>
       <c r="C170" s="10" t="n">
-        <v>10136823.61</v>
+        <v>10135180.49</v>
       </c>
       <c r="D170" s="10" t="n">
         <v>1511464.05</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>11648287.66</v>
+        <v>11646644.55</v>
       </c>
     </row>
     <row r="171">
@@ -3921,13 +3921,13 @@
         </is>
       </c>
       <c r="C173" s="10" t="n">
-        <v>10136823.61</v>
+        <v>10135180.49</v>
       </c>
       <c r="D173" s="10" t="n">
         <v>1511464.05</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>11648287.66</v>
+        <v>11646644.55</v>
       </c>
     </row>
     <row r="175">
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="C195" s="6" t="n">
-        <v>238298.31</v>
+        <v>238842.62</v>
       </c>
       <c r="D195" s="6" t="n">
-        <v>1259231.32</v>
+        <v>1260643.06</v>
       </c>
       <c r="E195" s="6" t="n">
-        <v>1497529.63</v>
+        <v>1499485.67</v>
       </c>
     </row>
     <row r="196">
@@ -4378,10 +4378,10 @@
         <v>0</v>
       </c>
       <c r="D196" s="8" t="n">
-        <v>428101</v>
+        <v>428815.2</v>
       </c>
       <c r="E196" s="8" t="n">
-        <v>428101</v>
+        <v>428815.2</v>
       </c>
     </row>
     <row r="197">
@@ -4417,13 +4417,13 @@
         </is>
       </c>
       <c r="C198" s="8" t="n">
-        <v>238298.31</v>
+        <v>238842.62</v>
       </c>
       <c r="D198" s="8" t="n">
         <v>357.36</v>
       </c>
       <c r="E198" s="8" t="n">
-        <v>238655.67</v>
+        <v>239199.98</v>
       </c>
     </row>
     <row r="199">
@@ -4462,10 +4462,10 @@
         <v>0</v>
       </c>
       <c r="D200" s="8" t="n">
-        <v>250973.23</v>
+        <v>251470.53</v>
       </c>
       <c r="E200" s="8" t="n">
-        <v>250973.23</v>
+        <v>251470.53</v>
       </c>
     </row>
     <row r="201">
@@ -4483,10 +4483,10 @@
         <v>0</v>
       </c>
       <c r="D201" s="8" t="n">
-        <v>100498.78</v>
+        <v>100699.02</v>
       </c>
       <c r="E201" s="8" t="n">
-        <v>100498.78</v>
+        <v>100699.02</v>
       </c>
     </row>
     <row r="202">
@@ -4728,13 +4728,13 @@
         </is>
       </c>
       <c r="C213" s="10" t="n">
-        <v>3007721.87</v>
+        <v>3008266.18</v>
       </c>
       <c r="D213" s="10" t="n">
-        <v>2082891.57</v>
+        <v>2084303.31</v>
       </c>
       <c r="E213" s="10" t="n">
-        <v>5090613.44</v>
+        <v>5092569.48</v>
       </c>
     </row>
     <row r="214">
@@ -4779,13 +4779,13 @@
         </is>
       </c>
       <c r="C216" s="10" t="n">
-        <v>3007721.87</v>
+        <v>3008266.18</v>
       </c>
       <c r="D216" s="10" t="n">
-        <v>2082891.57</v>
+        <v>2084303.31</v>
       </c>
       <c r="E216" s="10" t="n">
-        <v>5090613.44</v>
+        <v>5092569.48</v>
       </c>
     </row>
     <row r="218">
@@ -5212,13 +5212,13 @@
         </is>
       </c>
       <c r="C238" s="6" t="n">
-        <v>305904.41</v>
+        <v>311277.75</v>
       </c>
       <c r="D238" s="6" t="n">
-        <v>3278458.83</v>
+        <v>3305255.31</v>
       </c>
       <c r="E238" s="6" t="n">
-        <v>3584363.24</v>
+        <v>3616533.05</v>
       </c>
     </row>
     <row r="239">
@@ -5236,10 +5236,10 @@
         <v>0</v>
       </c>
       <c r="D239" s="8" t="n">
-        <v>808073.89</v>
+        <v>821630.15</v>
       </c>
       <c r="E239" s="8" t="n">
-        <v>808073.89</v>
+        <v>821630.15</v>
       </c>
     </row>
     <row r="240">
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="C241" s="8" t="n">
-        <v>305904.41</v>
+        <v>311277.75</v>
       </c>
       <c r="D241" s="8" t="n">
         <v>187427.05</v>
       </c>
       <c r="E241" s="8" t="n">
-        <v>493331.46</v>
+        <v>498704.8</v>
       </c>
     </row>
     <row r="242">
@@ -5320,10 +5320,10 @@
         <v>0</v>
       </c>
       <c r="D243" s="8" t="n">
-        <v>304967.62</v>
+        <v>314406.92</v>
       </c>
       <c r="E243" s="8" t="n">
-        <v>304967.62</v>
+        <v>314406.92</v>
       </c>
     </row>
     <row r="244">
@@ -5341,10 +5341,10 @@
         <v>0</v>
       </c>
       <c r="D244" s="8" t="n">
-        <v>122801.24</v>
+        <v>126602.17</v>
       </c>
       <c r="E244" s="8" t="n">
-        <v>122801.24</v>
+        <v>126602.17</v>
       </c>
     </row>
     <row r="245">
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="C256" s="10" t="n">
-        <v>20047394.21</v>
+        <v>20052767.54</v>
       </c>
       <c r="D256" s="10" t="n">
-        <v>11347334.47</v>
+        <v>11374130.95</v>
       </c>
       <c r="E256" s="10" t="n">
-        <v>31394728.67</v>
+        <v>31426898.49</v>
       </c>
     </row>
     <row r="257">
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="C259" s="10" t="n">
-        <v>20047394.21</v>
+        <v>20052767.54</v>
       </c>
       <c r="D259" s="10" t="n">
-        <v>11347334.47</v>
+        <v>11374130.95</v>
       </c>
       <c r="E259" s="10" t="n">
-        <v>31394728.67</v>
+        <v>31426898.49</v>
       </c>
     </row>
     <row r="261">
@@ -6070,13 +6070,13 @@
         </is>
       </c>
       <c r="C281" s="6" t="n">
-        <v>13683.49</v>
+        <v>13696.37</v>
       </c>
       <c r="D281" s="6" t="n">
-        <v>76157.28</v>
+        <v>76196.72</v>
       </c>
       <c r="E281" s="6" t="n">
-        <v>89840.77</v>
+        <v>89893.09</v>
       </c>
     </row>
     <row r="282">
@@ -6094,10 +6094,10 @@
         <v>0</v>
       </c>
       <c r="D282" s="8" t="n">
-        <v>38527.72</v>
+        <v>38547.67</v>
       </c>
       <c r="E282" s="8" t="n">
-        <v>38527.72</v>
+        <v>38547.67</v>
       </c>
     </row>
     <row r="283">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="C284" s="8" t="n">
-        <v>13683.49</v>
+        <v>13696.37</v>
       </c>
       <c r="D284" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E284" s="8" t="n">
-        <v>13683.49</v>
+        <v>13696.37</v>
       </c>
     </row>
     <row r="285">
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="D286" s="8" t="n">
-        <v>26827.1</v>
+        <v>26840.99</v>
       </c>
       <c r="E286" s="8" t="n">
-        <v>26827.1</v>
+        <v>26840.99</v>
       </c>
     </row>
     <row r="287">
@@ -6199,10 +6199,10 @@
         <v>0</v>
       </c>
       <c r="D287" s="8" t="n">
-        <v>10802.46</v>
+        <v>10808.06</v>
       </c>
       <c r="E287" s="8" t="n">
-        <v>10802.46</v>
+        <v>10808.06</v>
       </c>
     </row>
     <row r="288">
@@ -6444,13 +6444,13 @@
         </is>
       </c>
       <c r="C299" s="10" t="n">
-        <v>60528.02</v>
+        <v>60540.9</v>
       </c>
       <c r="D299" s="10" t="n">
-        <v>76157.28</v>
+        <v>76196.72</v>
       </c>
       <c r="E299" s="10" t="n">
-        <v>136685.3</v>
+        <v>136737.62</v>
       </c>
     </row>
     <row r="300">
@@ -6495,13 +6495,13 @@
         </is>
       </c>
       <c r="C302" s="10" t="n">
-        <v>60528.02</v>
+        <v>60540.9</v>
       </c>
       <c r="D302" s="10" t="n">
-        <v>76157.28</v>
+        <v>76196.72</v>
       </c>
       <c r="E302" s="10" t="n">
-        <v>136685.3</v>
+        <v>136737.62</v>
       </c>
     </row>
     <row r="304">
@@ -6928,13 +6928,13 @@
         </is>
       </c>
       <c r="C324" s="6" t="n">
-        <v>5046.26</v>
+        <v>5135</v>
       </c>
       <c r="D324" s="6" t="n">
-        <v>15513.28</v>
+        <v>15784.94</v>
       </c>
       <c r="E324" s="6" t="n">
-        <v>20559.54</v>
+        <v>20919.93</v>
       </c>
     </row>
     <row r="325">
@@ -6952,10 +6952,10 @@
         <v>0</v>
       </c>
       <c r="D325" s="8" t="n">
-        <v>7848.12</v>
+        <v>7985.55</v>
       </c>
       <c r="E325" s="8" t="n">
-        <v>7848.12</v>
+        <v>7985.55</v>
       </c>
     </row>
     <row r="326">
@@ -6991,13 +6991,13 @@
         </is>
       </c>
       <c r="C327" s="8" t="n">
-        <v>5046.26</v>
+        <v>5135</v>
       </c>
       <c r="D327" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E327" s="8" t="n">
-        <v>5046.26</v>
+        <v>5135</v>
       </c>
     </row>
     <row r="328">
@@ -7036,10 +7036,10 @@
         <v>0</v>
       </c>
       <c r="D329" s="8" t="n">
-        <v>5464.7</v>
+        <v>5560.39</v>
       </c>
       <c r="E329" s="8" t="n">
-        <v>5464.7</v>
+        <v>5560.39</v>
       </c>
     </row>
     <row r="330">
@@ -7057,10 +7057,10 @@
         <v>0</v>
       </c>
       <c r="D330" s="8" t="n">
-        <v>2200.47</v>
+        <v>2239</v>
       </c>
       <c r="E330" s="8" t="n">
-        <v>2200.47</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="331">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="C342" s="10" t="n">
-        <v>1516228.48</v>
+        <v>1516317.22</v>
       </c>
       <c r="D342" s="10" t="n">
-        <v>15513.28</v>
+        <v>15784.94</v>
       </c>
       <c r="E342" s="10" t="n">
-        <v>1531741.76</v>
+        <v>1532102.16</v>
       </c>
     </row>
     <row r="343">
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="C345" s="10" t="n">
-        <v>1516228.48</v>
+        <v>1516317.22</v>
       </c>
       <c r="D345" s="10" t="n">
-        <v>15513.28</v>
+        <v>15784.94</v>
       </c>
       <c r="E345" s="10" t="n">
-        <v>1531741.76</v>
+        <v>1532102.16</v>
       </c>
     </row>
   </sheetData>

--- a/data/informes/cuadro_10_5.xlsx
+++ b/data/informes/cuadro_10_5.xlsx
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>27495286.42</v>
+        <v>27474278.56</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>107371.84</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>27602658.26</v>
+        <v>27581650.4</v>
       </c>
     </row>
     <row r="6">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>19733139.54</v>
+        <v>19717106.75</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>19733139.54</v>
+        <v>19717106.75</v>
       </c>
     </row>
     <row r="7">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>4104709.61</v>
+        <v>4099734.54</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>4104709.61</v>
+        <v>4099734.54</v>
       </c>
     </row>
     <row r="10">
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>30297168.92</v>
+        <v>30276161.07</v>
       </c>
       <c r="D41" s="10" t="n">
         <v>4037645.27</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>34334814.19</v>
+        <v>34313806.34</v>
       </c>
     </row>
     <row r="42">
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>30297168.92</v>
+        <v>30276161.07</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>4037645.27</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>34334814.19</v>
+        <v>34313806.34</v>
       </c>
     </row>
     <row r="46">
@@ -1402,13 +1402,13 @@
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>40126098.66</v>
+        <v>40225250.7</v>
       </c>
       <c r="D48" s="6" t="n">
         <v>1011396.15</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>41137494.81</v>
+        <v>41236646.85</v>
       </c>
     </row>
     <row r="49">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>25880163.45</v>
+        <v>25983358.07</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>25880163.45</v>
+        <v>25983358.07</v>
       </c>
     </row>
     <row r="50">
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>4923733.26</v>
+        <v>4928708.33</v>
       </c>
       <c r="D52" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>4923733.26</v>
+        <v>4928708.33</v>
       </c>
     </row>
     <row r="53">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>2668423.44</v>
+        <v>2659405.79</v>
       </c>
       <c r="D53" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>2668423.44</v>
+        <v>2659405.79</v>
       </c>
     </row>
     <row r="54">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>40763973.76</v>
+        <v>40863125.79</v>
       </c>
       <c r="D84" s="10" t="n">
         <v>4537526.19</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>45301499.95</v>
+        <v>45400651.98</v>
       </c>
     </row>
     <row r="85">
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>40763973.76</v>
+        <v>40863125.79</v>
       </c>
       <c r="D87" s="10" t="n">
         <v>4537526.19</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>45301499.95</v>
+        <v>45400651.98</v>
       </c>
     </row>
     <row r="89">
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="C91" s="6" t="n">
-        <v>12685035.35</v>
+        <v>12679031.6</v>
       </c>
       <c r="D91" s="6" t="n">
         <v>994237.16</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>13679272.51</v>
+        <v>13673268.76</v>
       </c>
     </row>
     <row r="92">
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>5849601.49</v>
+        <v>5844380.86</v>
       </c>
       <c r="D92" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>5849601.49</v>
+        <v>5844380.86</v>
       </c>
     </row>
     <row r="93">
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>546838</v>
+        <v>546054.88</v>
       </c>
       <c r="D96" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>546838</v>
+        <v>546054.88</v>
       </c>
     </row>
     <row r="97">
@@ -3012,13 +3012,13 @@
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>14894145.32</v>
+        <v>14888141.57</v>
       </c>
       <c r="D127" s="10" t="n">
         <v>4314532.6</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>19208677.92</v>
+        <v>19202674.16</v>
       </c>
     </row>
     <row r="128">
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>14894145.32</v>
+        <v>14888141.57</v>
       </c>
       <c r="D130" s="10" t="n">
         <v>4314532.6</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>19208677.92</v>
+        <v>19202674.16</v>
       </c>
     </row>
     <row r="132">
@@ -3976,13 +3976,13 @@
         </is>
       </c>
       <c r="C177" s="6" t="n">
-        <v>2266836.5</v>
+        <v>2314286.27</v>
       </c>
       <c r="D177" s="6" t="n">
         <v>24069.71</v>
       </c>
       <c r="E177" s="6" t="n">
-        <v>2290906.21</v>
+        <v>2338355.98</v>
       </c>
     </row>
     <row r="178">
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="C178" s="8" t="n">
-        <v>45430.65</v>
+        <v>85555.19</v>
       </c>
       <c r="D178" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E178" s="8" t="n">
-        <v>45430.65</v>
+        <v>85555.19</v>
       </c>
     </row>
     <row r="179">
@@ -4081,13 +4081,13 @@
         </is>
       </c>
       <c r="C182" s="8" t="n">
-        <v>238.14</v>
+        <v>7563.38</v>
       </c>
       <c r="D182" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E182" s="8" t="n">
-        <v>238.14</v>
+        <v>7563.38</v>
       </c>
     </row>
     <row r="183">
@@ -4728,13 +4728,13 @@
         </is>
       </c>
       <c r="C213" s="10" t="n">
-        <v>3008266.18</v>
+        <v>3055715.95</v>
       </c>
       <c r="D213" s="10" t="n">
         <v>2084303.31</v>
       </c>
       <c r="E213" s="10" t="n">
-        <v>5092569.48</v>
+        <v>5140019.25</v>
       </c>
     </row>
     <row r="214">
@@ -4779,13 +4779,13 @@
         </is>
       </c>
       <c r="C216" s="10" t="n">
-        <v>3008266.18</v>
+        <v>3055715.95</v>
       </c>
       <c r="D216" s="10" t="n">
         <v>2084303.31</v>
       </c>
       <c r="E216" s="10" t="n">
-        <v>5092569.48</v>
+        <v>5140019.25</v>
       </c>
     </row>
     <row r="218">
@@ -4834,13 +4834,13 @@
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>19092807.67</v>
+        <v>19116824.11</v>
       </c>
       <c r="D220" s="6" t="n">
         <v>279076.91</v>
       </c>
       <c r="E220" s="6" t="n">
-        <v>19371884.58</v>
+        <v>19395901.02</v>
       </c>
     </row>
     <row r="221">
@@ -4855,13 +4855,13 @@
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>1473887.3</v>
+        <v>1495428.21</v>
       </c>
       <c r="D221" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E221" s="8" t="n">
-        <v>1473887.3</v>
+        <v>1495428.21</v>
       </c>
     </row>
     <row r="222">
@@ -4939,13 +4939,13 @@
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>164838.09</v>
+        <v>167313.63</v>
       </c>
       <c r="D225" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E225" s="8" t="n">
-        <v>164838.09</v>
+        <v>167313.63</v>
       </c>
     </row>
     <row r="226">
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="C256" s="10" t="n">
-        <v>20052767.54</v>
+        <v>20076783.98</v>
       </c>
       <c r="D256" s="10" t="n">
         <v>11374130.95</v>
       </c>
       <c r="E256" s="10" t="n">
-        <v>31426898.49</v>
+        <v>31450914.93</v>
       </c>
     </row>
     <row r="257">
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="C259" s="10" t="n">
-        <v>20052767.54</v>
+        <v>20076783.98</v>
       </c>
       <c r="D259" s="10" t="n">
         <v>11374130.95</v>
       </c>
       <c r="E259" s="10" t="n">
-        <v>31426898.49</v>
+        <v>31450914.93</v>
       </c>
     </row>
     <row r="261">
